--- a/output/pdf_financials_xlsx/NGC.xlsx
+++ b/output/pdf_financials_xlsx/NGC.xlsx
@@ -5863,7 +5863,7 @@
         <v>3.242503</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>4.946831</v>
+        <v>1.86259</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>2.605915</v>
@@ -5872,7 +5872,7 @@
         <v>2.658904</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.130029</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>2.907743</v>
@@ -6481,19 +6481,19 @@
         <v>-0.035161</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0.024399</v>
+        <v>-0.04</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>-5.29</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>0.731</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="R103" s="3" t="n">
-        <v>0</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="104">
@@ -6655,19 +6655,19 @@
         <v>0.016135</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>1.413399</v>
+        <v>1.349</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-4.59</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>4.874</v>
+        <v>5.605</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>5.374</v>
+        <v>5.905</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>6.581</v>
+        <v>6.845</v>
       </c>
     </row>
     <row r="107">
@@ -7324,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>7.08175</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-3.000273</v>
@@ -19613,7 +19613,11 @@
           <t>Warrants reserves (note 7)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -21494,7 +21498,11 @@
           <t>Warrant reserves 13</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -26888,7 +26896,11 @@
           <t>Receivables, prepaids and deposits</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -46325,7 +46337,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -46422,7 +46438,11 @@
           <t>Warrants issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NGC.xlsx
+++ b/output/pdf_financials_xlsx/NGC.xlsx
@@ -953,19 +953,19 @@
         <v>0.792307</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>3.660799</v>
+        <v>3.646</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>7.778</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>11.414</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>8.670999999999999</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>8.635</v>
       </c>
     </row>
     <row r="11">
@@ -1033,55 +1033,55 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.08247599999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000864</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.027614</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.051669</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.071351</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.031892</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.012199</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.005581</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.017282</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.055384</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.04136</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.011605</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.159</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.075</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.169</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.054</v>
       </c>
     </row>
     <row r="13">
@@ -1981,55 +1981,55 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.101824</v>
+        <v>-3.1843</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.382037</v>
+        <v>-4.382901</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.744966</v>
+        <v>-1.77258</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.45753</v>
+        <v>-2.509199</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.493512</v>
+        <v>-1.564863</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.990734</v>
+        <v>-1.022626</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.036275</v>
+        <v>-1.048474</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.673793</v>
+        <v>-1.679374</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.897177</v>
+        <v>-0.914459</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.03729</v>
+        <v>-1.092674</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.609062</v>
+        <v>-0.6504219999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.868131</v>
+        <v>-0.879736</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.226</v>
+        <v>-3.204</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-14.551</v>
+        <v>-14.392</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-23.643</v>
+        <v>-23.568</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-38.804</v>
+        <v>-38.635</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-21.309</v>
+        <v>-21.255</v>
       </c>
     </row>
     <row r="28">
@@ -2097,55 +2097,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.101824</v>
+        <v>-3.1843</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.382037</v>
+        <v>-4.382901</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.744966</v>
+        <v>-1.77258</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.45753</v>
+        <v>-2.509199</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.425408</v>
+        <v>-1.496759</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.921638</v>
+        <v>-0.95353</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.967179</v>
+        <v>-0.979378</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.612685</v>
+        <v>-1.618266</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.86033</v>
+        <v>-0.8776119999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.002477</v>
+        <v>-1.057861</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.573987</v>
+        <v>-0.615347</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.833951</v>
+        <v>-0.845556</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.195</v>
+        <v>-3.173</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-11.779</v>
+        <v>-11.62</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-20.401</v>
+        <v>-20.326</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-33.46</v>
+        <v>-33.291</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-14.384</v>
+        <v>-14.33</v>
       </c>
     </row>
     <row r="30">
@@ -2220,16 +2220,16 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-98.215625781706</v>
+        <v>-96.88985241390812</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-119.3110708228551</v>
+        <v>-118.8724486812094</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-147.2192889827526</v>
+        <v>-146.4757127771911</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-74.79590244917061</v>
+        <v>-74.51510581873018</v>
       </c>
     </row>
     <row r="31">
@@ -2388,13 +2388,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.103345</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.08146299999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.315011</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.298934</v>
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.103345</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.550675</v>
+        <v>0.632138</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>3.617487</v>
+        <v>3.932498</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>4.152888</v>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.123007</v>
+        <v>0.019662</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.114977</v>
+        <v>0.033514</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.47377</v>
+        <v>0.158759</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.103536</v>
@@ -7706,16 +7706,16 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-3.272</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.575</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.448</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="125">
@@ -7764,16 +7764,16 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-3.272</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.575</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.448</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="126">
@@ -9755,7 +9755,11 @@
           <t>Restricted cash and reclamation deposits 5, 30</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -13147,7 +13151,11 @@
           <t>Restricted cash and reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -14828,7 +14836,11 @@
           <t>Restricted cash and reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15030,7 +15042,11 @@
           <t>Restricted cash and reclamation deposits 5, 29</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -16891,7 +16907,11 @@
           <t>Reclamation deposit (note 15)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -18263,7 +18283,11 @@
           <t>Reclamation deposit (note 13)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -19225,7 +19249,11 @@
           <t>Reclamation deposit (note 14)</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -22296,7 +22324,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -23999,7 +24027,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
@@ -28274,7 +28302,11 @@
           <t>Lease payments 18</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -32375,7 +32407,11 @@
           <t>Deposit and lease payments 18</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -45838,7 +45874,11 @@
           <t>(Increase) in reclamation deposit</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -56335,7 +56375,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -57040,7 +57080,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -59430,7 +59470,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -60018,7 +60058,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -64530,7 +64570,7 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -76371,7 +76411,7 @@
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E684" s="5" t="n">

--- a/output/pdf_financials_xlsx/NGC.xlsx
+++ b/output/pdf_financials_xlsx/NGC.xlsx
@@ -767,19 +767,19 @@
         <v>0.618783</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.172944</v>
+        <v>0.641039</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.205238</v>
+        <v>0.677312</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.064474</v>
+        <v>0.47954</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.113235</v>
+        <v>0.444506</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.289307</v>
+        <v>1.048467</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>0.5576</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-18.791852</v>
+        <v>21.249382</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>26.55191</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>8.321301999999999</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -2248,13 +2248,13 @@
         <v>-31.95477734236656</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-764.6641953506163</v>
+        <v>-864.6641953506162</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-1777.81698439651</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-839.9128323041301</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -6341,31 +6341,31 @@
         <v>-0.372644</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-1.070111</v>
+        <v>0.050824</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>1.570041</v>
+        <v>0.06758500000000001</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.021512</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005552</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.001605</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.035657</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.032467</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.002522</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>-0.063915</v>
       </c>
       <c r="O101" s="3" t="n">
         <v>0</v>
@@ -6631,31 +6631,31 @@
         <v>0.206478</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-1.135957</v>
+        <v>-0.015022</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>1.645515</v>
+        <v>0.143059</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.012712</v>
+        <v>0.034224</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.131192</v>
+        <v>-0.136744</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.006069</v>
+        <v>0.007674</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.07482</v>
+        <v>-0.110477</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.098066</v>
+        <v>-0.065599</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.016135</v>
+        <v>0.018657</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>1.349</v>
+        <v>1.285085</v>
       </c>
       <c r="O106" s="3" t="n">
         <v>-9.880000000000001</v>
@@ -6713,7 +6713,7 @@
         <v>0.202125</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0.844</v>
+        <v>1.689</v>
       </c>
       <c r="O107" s="3" t="n">
         <v>1.654</v>
@@ -6909,22 +6909,22 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00585</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07076200000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.1338</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.541434</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>0.01831</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -8048,20 +8048,14 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.037213</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.103345</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.08146299999999999</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0.315011</v>
@@ -8236,20 +8230,14 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.103345</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.08146299999999999</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.315011</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>1.298934</v>
@@ -8309,22 +8297,22 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00585</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07076200000000001</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.1338</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.541434</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01831</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8377,16 +8365,16 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.153202</v>
+        <v>-1.223964</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-12.909689</v>
+        <v>-13.043489</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.441943</v>
+        <v>-1.983377</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.787609</v>
+        <v>-0.8059190000000001</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.663201</v>
@@ -31914,7 +31902,11 @@
           <t>Private placement 19</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -40310,7 +40302,11 @@
           <t>Share based payment expense - - - 845 -</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -41100,7 +41096,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -44254,7 +44254,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -44747,7 +44751,11 @@
           <t>Issuance of share capital in private placement</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -46583,7 +46591,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -47688,7 +47700,11 @@
           <t>Net sale (purchase) of equipment</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -47985,7 +48001,11 @@
           <t>Gross proceeds for shares to be issued in a future private placement</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E398" t="inlineStr">
         <is>
           <t>-</t>
@@ -48690,7 +48710,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -49688,7 +49712,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -50680,7 +50708,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E425" s="5" t="n">
         <v>0.037213</v>
       </c>
@@ -50775,7 +50807,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -53292,7 +53328,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E451" s="5" t="n">
         <v>-0.8169999999999999</v>
       </c>
@@ -54296,7 +54336,11 @@
           <t>Cash at end of the year $</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E461" s="5" t="n">
         <v>0.103345</v>
       </c>
@@ -54898,7 +54942,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E467" s="5" t="n">
         <v>-0.00585</v>
       </c>
@@ -63794,7 +63842,11 @@
           <t>Office, management and director fees (note 13)</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -66332,7 +66384,11 @@
           <t>Office, management and director fees (note 11)</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr">
         <is>
           <t>-</t>
@@ -67520,7 +67576,11 @@
           <t>Office, management and director fees (note 9)</t>
         </is>
       </c>
-      <c r="D595" t="inlineStr"/>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E595" t="inlineStr">
         <is>
           <t>-</t>
@@ -73920,7 +73980,11 @@
           <t>Loss before deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr"/>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E659" t="inlineStr">
         <is>
           <t>-</t>
@@ -74017,7 +74081,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr"/>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E660" t="inlineStr">
         <is>
           <t>-</t>
